--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1131,472 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130008195</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>470697</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackade i ett träd, flög sen västerut över vägen.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130004636</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>470625</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539091</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130008210</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>470630</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6539099</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid p-fickan på vägen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130008114</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>470668</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6539090</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska födohack på låga av tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,6 +1597,123 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130017109</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>470661</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6539022</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska spår/ringhack på tall 5 m väst om.vägen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1252,7 +1252,7 @@
         <v>130004636</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1719,7 +1719,7 @@
         <v>130111287</v>
       </c>
       <c r="B11" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>130008195</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>130004636</v>
       </c>
       <c r="B7" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>130008210</v>
       </c>
       <c r="B8" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>130008114</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>130017109</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>130111287</v>
       </c>
       <c r="B11" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1719,7 +1719,7 @@
         <v>130111287</v>
       </c>
       <c r="B11" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>130008210</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>130111287</v>
       </c>
       <c r="B11" t="n">
-        <v>97797</v>
+        <v>97823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>130008210</v>
       </c>
       <c r="B8" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>130008210</v>
       </c>
       <c r="B8" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>130008210</v>
       </c>
       <c r="B8" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129464319</v>
+        <v>130324988</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470689</v>
+        <v>470736</v>
       </c>
       <c r="R2" t="n">
-        <v>6539049</v>
+        <v>6539110</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,27 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska spår högst upp, äldre spår längst ner. Träder påvisar förekomst över längre tid o nutid</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,27 +791,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129462682</v>
+        <v>130008089</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,14 +827,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470686</v>
+        <v>470720</v>
       </c>
       <c r="R3" t="n">
-        <v>6538986</v>
+        <v>6539108</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,27 +861,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 tallar bredvid varandra, bägge m färska spår</t>
+          <t>Färska födohack på klen granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,39 +896,39 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129462512</v>
+        <v>130008114</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,14 +944,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470664</v>
+        <v>470668</v>
       </c>
       <c r="R4" t="n">
-        <v>6538981</v>
+        <v>6539090</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -979,22 +978,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,39 +1013,39 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129462597</v>
+        <v>130008195</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,22 +1053,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470673</v>
+        <v>470697</v>
       </c>
       <c r="R5" t="n">
-        <v>6538997</v>
+        <v>6539001</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,22 +1094,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackade i ett träd, flög sen västerut över vägen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130008195</v>
+        <v>129462512</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,16 +1152,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1161,21 +1169,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470697</v>
+        <v>470664</v>
       </c>
       <c r="R6" t="n">
-        <v>6539001</v>
+        <v>6538981</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,27 +1211,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackade i ett träd, flög sen västerut över vägen.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130004636</v>
+        <v>129462597</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,43 +1264,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470625</v>
+        <v>470673</v>
       </c>
       <c r="R7" t="n">
-        <v>6539091</v>
+        <v>6538997</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,62 +1353,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130008210</v>
+        <v>129462682</v>
       </c>
       <c r="B8" t="n">
-        <v>57073</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470630</v>
+        <v>470686</v>
       </c>
       <c r="R8" t="n">
-        <v>6539099</v>
+        <v>6538986</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1435,27 +1435,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid p-fickan på vägen.</t>
+          <t>2 tallar bredvid varandra, bägge m färska spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130008114</v>
+        <v>129464319</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,16 +1493,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,14 +1518,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470668</v>
+        <v>470689</v>
       </c>
       <c r="R9" t="n">
-        <v>6539090</v>
+        <v>6539049</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1552,27 +1552,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Färska spår högst upp, äldre spår längst ner. Träder påvisar förekomst över längre tid o nutid</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,12 +1587,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         <v>130017109</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130111287</v>
+        <v>130008210</v>
       </c>
       <c r="B11" t="n">
-        <v>97823</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,34 +1727,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470734</v>
+        <v>470630</v>
       </c>
       <c r="R11" t="n">
-        <v>6539068</v>
+        <v>6539099</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1781,22 +1786,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid p-fickan på vägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,6 +1830,345 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129462997</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>470576</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6539029</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hördes tydligt när andra mesar varnade.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130004636</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>470625</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6539091</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130111287</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>470734</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6539068</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60587-2025 artfynd.xlsx
+++ b/artfynd/A 60587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324988</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130008089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130008114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130008195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462597</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462682</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,6 +1636,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464319</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1713,6 +1758,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017109</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1830,6 +1880,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130008210</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1946,6 +2001,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2062,6 +2122,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130004636</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2169,8 +2234,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111287</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>